--- a/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt1_rubricas.xlsx
@@ -1788,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E877BB74-96C3-4BCF-A92D-E92029FF0AF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A292EF89-E312-4169-BD9E-87ACC0EA43F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E0337E-50BE-4CB3-8FD0-94A04B1DE8BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2BF4C5-CF81-4A8C-8CBE-4C688D8F8790}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4D3521-E48A-4D4B-9D37-9BBFF2D78370}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4332A377-1F1D-461F-9A29-A979581B6396}"/>
 </file>